--- a/output/身体拘束廃止に関する指針_いいかいご.xlsx
+++ b/output/身体拘束廃止に関する指針_いいかいご.xlsx
@@ -751,21 +751,21 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・代表取締役（法人代表者）</t>
+          <t xml:space="preserve">　・代表取締役（法人代表者）　吉田 駿成</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・管理者</t>
+          <t xml:space="preserve">　・管理者（委員長）　生田 友哉</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・サービス提供責任者</t>
+          <t xml:space="preserve">　・必要に応じて、サービス提供責任者・担当訪問介護員等の参加を求める</t>
         </is>
       </c>
     </row>

--- a/output/身体拘束廃止に関する指針_いいかいご.xlsx
+++ b/output/身体拘束廃止に関する指針_いいかいご.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -751,489 +751,503 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・代表取締役（法人代表者）　吉田 駿成</t>
+          <t xml:space="preserve">　・管理者（委員長）　生田 友哉</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・管理者（委員長）　生田 友哉</t>
+          <t xml:space="preserve">　・代表取締役（法人代表者）　吉田 俊輔</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・必要に応じて、サービス提供責任者・担当訪問介護員等の参加を求める</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="8" customHeight="1"/>
+          <t xml:space="preserve">　・事務・総務　吉田 麻美</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・訪問介護員（ヘルパー代表）　WIN YADANAR AWNG</t>
+        </is>
+      </c>
+    </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・必要に応じて、担当訪問介護員・ケアマネジャー・主治医等の参加を求める</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="8" customHeight="1"/>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>③ 委員会の開催</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="48" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
+    <row r="74" ht="48" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>年1回以上定期的に開催するほか、必要時に随時開催します。開催はテレビ電話装置等を活用して行うことができ、虐待防止委員会等と一体的に開催することを妨げません。結果は記録し、全職員に周知します。</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="10" customHeight="1"/>
-    <row r="74" ht="26" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
+    <row r="75" ht="10" customHeight="1"/>
+    <row r="76" ht="26" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>4．やむを得ず身体拘束を行う場合の対応</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>本人又は他の利用者等の生命又は身体を保護するための措置として、緊急やむを得ず身体拘束を行わなければならない場合は、以下の手順に従って実施します。</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="6" customHeight="1"/>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
+    <row r="78" ht="6" customHeight="1"/>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>1）カンファレンスの実施</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="48" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
+    <row r="80" ht="48" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>緊急やむを得ない状況になった場合、委員会の構成員が集まり、拘束による利用者の心身の損害や拘束をしない場合のリスクについて検討し、身体拘束を行う事を選択する前に①切迫性②非代替性③一時性の3要件全てを満たしているかどうかについて検討、確認します。</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="64" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
+    <row r="81" ht="64" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>要件を検討・確認した上で、身体拘束を行うことを選択した場合は、拘束の方法、場所、時間帯、期間等について検討し、本人・家族に対する説明書を作成します。また、廃止に向けた取り組み改善の検討会を早急に行い実施に努めます。居宅介護支援事業所（ケアマネジャー）にも報告し、ケアプランへの位置づけについて協議します。</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="6" customHeight="1"/>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
+    <row r="82" ht="6" customHeight="1"/>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>2）利用者本人や家族に対しての説明</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="32" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>身体拘束の内容・目的・理由・拘束時間又は時間帯・期間・場所・改善に向けた取り組み方法を詳細に説明し、充分理解が得られるように努めます。</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>また、身体拘束の同意期限を越え、なお拘束を必要とする場合については、事前に契約者・家族等と行っている内容と方向性、利用者の状態などを確認説明し、同意を得たうえで実施します。</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="6" customHeight="1"/>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
+    <row r="86" ht="6" customHeight="1"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>3）記録と再検討</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="64" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
+    <row r="88" ht="64" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>法律上、身体拘束に関する記録は義務付けられており、専用の様式を用いてその態様及び時間・その際の利用者の心身の状況・やむを得なかった理由などを記録します。身体拘束の早期解除に向けて、拘束の必要性や方法を逐次検討します。その記録は5年間保存し、行政担当部局の運営指導等が行われる際に提示できるようにします。</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="6" customHeight="1"/>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
+    <row r="89" ht="6" customHeight="1"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>4）拘束の解除</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="32" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>3）の記録と再検討の結果、身体拘束を継続する必要性がなくなった場合は、速やかに身体拘束を解除します。その場合には、契約者、家族、居宅介護支援事業所に報告します。</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="10" customHeight="1"/>
-    <row r="91" ht="26" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
+    <row r="92" ht="10" customHeight="1"/>
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>5．身体的拘束等の報告方法等のための方策に関する基本方針</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="32" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
+    <row r="94" ht="32" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　1）身体的拘束等を行う場合には、4．の手続きに基づき利用者家族に速やかに説明し、報告を行うこと。</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="48" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
+    <row r="95" ht="48" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　2）訪問先等において他の職員等による適切な手続きに依らない身体的拘束等を視認等した場合、具体的な状況、時刻等を確認したうえで委員会への報告を行うこと。当該報告を受けた委員は、身体的拘束を実施したと思われる職員に聞き取りを行い実態の把握に努めること。</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="48" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="96" ht="48" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　3）適切な手続きに依らない身体的拘束の事実が判明した場合は、利用者及び利用者家族への謝罪を行い、大阪市への報告を行うこと。高齢者虐待に該当するおそれがある場合は、高齢者虐待防止法に基づき通報すること。</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="32" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
+    <row r="97" ht="32" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　4）訪問時に家族等による身体拘束を発見した場合は、管理者に報告し、居宅介護支援事業所と連携して対応すること。</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="8" customHeight="1"/>
-    <row r="97" ht="22" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
+    <row r="98" ht="8" customHeight="1"/>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>介護保険指定基準において身体拘束禁止の対象となる具体的な行為</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（1）徘徊しないように、車椅子や椅子・ベッドに体幹や四肢をひも等で縛る</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（2）転落しないように、ベッドに体幹や四肢をひも等で縛る</t>
         </is>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（3）自分で降りられないように、ベッドを柵（サイドレール）で囲む</t>
+          <t xml:space="preserve">　（1）徘徊しないように、車椅子や椅子・ベッドに体幹や四肢をひも等で縛る</t>
         </is>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　（2）転落しないように、ベッドに体幹や四肢をひも等で縛る</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（3）自分で降りられないように、ベッドを柵（サイドレール）で囲む</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　（4）点滴・経管栄養等のチューブを抜かないように、四肢をひも等で縛る</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="32" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　（5）点滴・経管栄養等のチューブを抜かないように、又は皮膚をかきむしらないように、手指の機能を制限するミトン型の手袋等をつける</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="32" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　（6）車椅子・椅子からずり落ちたり、立ち上がったりしないように、Y字型拘束帯や腰ベルト・車椅子テーブルをつける</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（7）立ち上がる能力のある人の立ち上がりを妨げるような椅子を使用する</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（8）脱衣やオムツはずしを制限するために、介護衣（つなぎ服）を着せる</t>
         </is>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（9）他人への迷惑行為を防ぐために、ベッドなどに体幹や四肢をひも等で縛る</t>
+          <t xml:space="preserve">　（7）立ち上がる能力のある人の立ち上がりを妨げるような椅子を使用する</t>
         </is>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（10）行動を落ち着かせるために、向精神薬を過剰に服用させる</t>
+          <t xml:space="preserve">　（8）脱衣やオムツはずしを制限するために、介護衣（つなぎ服）を着せる</t>
         </is>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　（9）他人への迷惑行為を防ぐために、ベッドなどに体幹や四肢をひも等で縛る</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（10）行動を落ち着かせるために、向精神薬を過剰に服用させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　（11）自分の意思で開けることのできない居室等に隔離する</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="8" customHeight="1"/>
-    <row r="110" ht="26" customHeight="1">
-      <c r="A110" s="4" t="inlineStr">
+    <row r="111" ht="8" customHeight="1"/>
+    <row r="112" ht="26" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>6．身体拘束廃止に向けた各職種の役割</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="32" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
+    <row r="113" ht="32" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>身体拘束の廃止のために、各職種の専門性に基づくアプローチから、チームケアを行うことを基本とし、それぞれの果たすべき役割に責任をもって対応します。</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="6" customHeight="1"/>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="7" t="inlineStr">
+    <row r="114" ht="6" customHeight="1"/>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="7" t="inlineStr">
         <is>
           <t>（代表取締役）</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1）身体拘束における諸課題等の最高責任者</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　2）委員会総括責任者</t>
         </is>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　1）身体拘束における諸課題等の最高責任者</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2）委員会総括責任者</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　3）家族、医療、行政機関、その他関係機関への対応</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="8" customHeight="1"/>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="7" t="inlineStr">
+    <row r="119" ht="8" customHeight="1"/>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="7" t="inlineStr">
         <is>
           <t>（身体拘束適正化委員会）</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1）身体拘束廃止のための指針の周知徹底</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　2）身体拘束に関する説明書、システムの確立</t>
         </is>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　3）身体拘束に関する対応策及び防止策の検討</t>
+          <t xml:space="preserve">　1）身体拘束廃止のための指針の周知徹底</t>
         </is>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　4）検討内容の実践、結果確認及び再検討</t>
+          <t xml:space="preserve">　2）身体拘束に関する説明書、システムの確立</t>
         </is>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　3）身体拘束に関する対応策及び防止策の検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4）検討内容の実践、結果確認及び再検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　5）身体拘束廃止に向けた職員教育</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="8" customHeight="1"/>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="7" t="inlineStr">
+    <row r="126" ht="8" customHeight="1"/>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="7" t="inlineStr">
         <is>
           <t>（全従業者）</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1）拘束がもたらす弊害を正確に認識する</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　2）利用者の尊厳を理解する</t>
         </is>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　3）利用者の疾病、障害等による行動特性の理解</t>
+          <t xml:space="preserve">　1）拘束がもたらす弊害を正確に認識する</t>
         </is>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　4）利用者個々の心身の状態を把握し、基本的ケアに努める</t>
+          <t xml:space="preserve">　2）利用者の尊厳を理解する</t>
         </is>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　5）利用者とのコミュニケーションを充分にとる</t>
+          <t xml:space="preserve">　3）利用者の疾病、障害等による行動特性の理解</t>
         </is>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　6）記録は正確かつ丁寧に記録する</t>
+          <t xml:space="preserve">　4）利用者個々の心身の状態を把握し、基本的ケアに努める</t>
         </is>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　7）医療機関、家族、居宅介護支援事業所等の関係機関との連絡調整</t>
+          <t xml:space="preserve">　5）利用者とのコミュニケーションを充分にとる</t>
         </is>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　8）訪問介護員が行える医療的ケアの範囲の確認</t>
+          <t xml:space="preserve">　6）記録は正確かつ丁寧に記録する</t>
         </is>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　9）重度化する利用者の状態観察</t>
+          <t xml:space="preserve">　7）医療機関、家族、居宅介護支援事業所等の関係機関との連絡調整</t>
         </is>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　10）家族の意向に添ったケアの確立</t>
+          <t xml:space="preserve">　8）訪問介護員が行える医療的ケアの範囲の確認</t>
         </is>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　9）重度化する利用者の状態観察</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　10）家族の意向に添ったケアの確立</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　11）利用者宅の住環境（段差・家具配置等）や福祉用具の改善提案</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="8" customHeight="1"/>
-    <row r="138" ht="26" customHeight="1">
-      <c r="A138" s="4" t="inlineStr">
+    <row r="139" ht="8" customHeight="1"/>
+    <row r="140" ht="26" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
         <is>
           <t>7．身体拘束廃止・改善のための職員教育・研修</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="32" customHeight="1">
-      <c r="A139" s="5" t="inlineStr">
+    <row r="141" ht="32" customHeight="1">
+      <c r="A141" s="5" t="inlineStr">
         <is>
           <t>支援に携わる全ての職員（登録ヘルパーを含む）に対して、身体拘束廃止と人権を尊重したケアの励行を図り、事故防止と合わせてリスクマネジメントとしての職員教育を行います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　① 定期的な教育・研修（年2回）の実施</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　② 新任者に対する身体拘束廃止・改善のための研修の実施</t>
         </is>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　① 定期的な教育・研修（年2回）の実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② 新任者に対する身体拘束廃止・改善のための研修の実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　③ その他必要な教育・研修の実施</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="8" customHeight="1"/>
-    <row r="144" ht="26" customHeight="1">
-      <c r="A144" s="4" t="inlineStr">
+    <row r="145" ht="8" customHeight="1"/>
+    <row r="146" ht="26" customHeight="1">
+      <c r="A146" s="4" t="inlineStr">
         <is>
           <t>8．身体拘束廃止に関する指針の閲覧について</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="32" customHeight="1">
-      <c r="A145" s="5" t="inlineStr">
+    <row r="147" ht="32" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
         <is>
           <t>この指針は、当事業所内に掲示するとともに、利用者・家族がいつでも自由に閲覧することができます。</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="10" customHeight="1"/>
-    <row r="147" ht="26" customHeight="1">
-      <c r="A147" s="4" t="inlineStr">
+    <row r="148" ht="10" customHeight="1"/>
+    <row r="149" ht="26" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
         <is>
           <t>9．附則</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="5" t="inlineStr">
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>この指針は令和8年2月1日より施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="102">
+  <mergeCells count="104">
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A142:E142"/>
     <mergeCell ref="A1:E1"/>
@@ -1241,15 +1255,15 @@
     <mergeCell ref="A94:E94"/>
     <mergeCell ref="A103:E103"/>
     <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
     <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A137:E137"/>
     <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A89:E89"/>
     <mergeCell ref="A136:E136"/>
     <mergeCell ref="A105:E105"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A113:E113"/>
-    <mergeCell ref="A139:E139"/>
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="A129:E129"/>
     <mergeCell ref="A91:E91"/>
@@ -1263,17 +1277,14 @@
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A83:E83"/>
-    <mergeCell ref="A148:E148"/>
     <mergeCell ref="A49:E49"/>
     <mergeCell ref="A138:E138"/>
     <mergeCell ref="A132:E132"/>
     <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A119:E119"/>
     <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A78:E78"/>
     <mergeCell ref="A118:E118"/>
-    <mergeCell ref="A75:E75"/>
     <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A80:E80"/>
     <mergeCell ref="A120:E120"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A104:E104"/>
@@ -1283,59 +1294,64 @@
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A81:E81"/>
     <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A96:E96"/>
     <mergeCell ref="A147:E147"/>
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A73:E73"/>
     <mergeCell ref="A60:E60"/>
     <mergeCell ref="A123:E123"/>
     <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A146:E146"/>
+    <mergeCell ref="A124:E124"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A84:E84"/>
     <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A149:E149"/>
     <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A86:E86"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A141:E141"/>
     <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A150:E150"/>
     <mergeCell ref="A144:E144"/>
     <mergeCell ref="A122:E122"/>
     <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A72:E72"/>
     <mergeCell ref="A134:E134"/>
+    <mergeCell ref="A112:E112"/>
     <mergeCell ref="A121:E121"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="A127:E127"/>
     <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A114:E114"/>
     <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A98:E98"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A107:E107"/>
     <mergeCell ref="A61:E61"/>
     <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
     <mergeCell ref="A99:E99"/>
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A145:E145"/>
     <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A85:E85"/>
     <mergeCell ref="A116:E116"/>
-    <mergeCell ref="A126:E126"/>
     <mergeCell ref="A140:E140"/>
     <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A109:E109"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A62:E62"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A111:E111"/>
-    <mergeCell ref="A92:E92"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A143:E143"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/身体拘束廃止に関する指針_いいかいご.xlsx
+++ b/output/身体拘束廃止に関する指針_いいかいご.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E150"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -772,498 +772,505 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・訪問介護員（ヘルパー代表）　WIN YADANAR AWNG</t>
+          <t xml:space="preserve">　・訪問介護員　松村 知恵</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　・訪問介護員（ヘルパー代表）　WIN YADANAR AWNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　・必要に応じて、担当訪問介護員・ケアマネジャー・主治医等の参加を求める</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="8" customHeight="1"/>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
+    <row r="73" ht="8" customHeight="1"/>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>③ 委員会の開催</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="48" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
+    <row r="75" ht="48" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>年1回以上定期的に開催するほか、必要時に随時開催します。開催はテレビ電話装置等を活用して行うことができ、虐待防止委員会等と一体的に開催することを妨げません。結果は記録し、全職員に周知します。</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="10" customHeight="1"/>
-    <row r="76" ht="26" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
+    <row r="76" ht="10" customHeight="1"/>
+    <row r="77" ht="26" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>4．やむを得ず身体拘束を行う場合の対応</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>本人又は他の利用者等の生命又は身体を保護するための措置として、緊急やむを得ず身体拘束を行わなければならない場合は、以下の手順に従って実施します。</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="6" customHeight="1"/>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
+    <row r="79" ht="6" customHeight="1"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>1）カンファレンスの実施</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="48" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
+    <row r="81" ht="48" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>緊急やむを得ない状況になった場合、委員会の構成員が集まり、拘束による利用者の心身の損害や拘束をしない場合のリスクについて検討し、身体拘束を行う事を選択する前に①切迫性②非代替性③一時性の3要件全てを満たしているかどうかについて検討、確認します。</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="64" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
+    <row r="82" ht="64" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>要件を検討・確認した上で、身体拘束を行うことを選択した場合は、拘束の方法、場所、時間帯、期間等について検討し、本人・家族に対する説明書を作成します。また、廃止に向けた取り組み改善の検討会を早急に行い実施に努めます。居宅介護支援事業所（ケアマネジャー）にも報告し、ケアプランへの位置づけについて協議します。</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="6" customHeight="1"/>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
+    <row r="83" ht="6" customHeight="1"/>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>2）利用者本人や家族に対しての説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>身体拘束の内容・目的・理由・拘束時間又は時間帯・期間・場所・改善に向けた取り組み方法を詳細に説明し、充分理解が得られるように努めます。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="32" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
         <is>
+          <t>身体拘束の内容・目的・理由・拘束時間又は時間帯・期間・場所・改善に向けた取り組み方法を詳細に説明し、充分理解が得られるように努めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
           <t>また、身体拘束の同意期限を越え、なお拘束を必要とする場合については、事前に契約者・家族等と行っている内容と方向性、利用者の状態などを確認説明し、同意を得たうえで実施します。</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="6" customHeight="1"/>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
+    <row r="87" ht="6" customHeight="1"/>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>3）記録と再検討</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="64" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
+    <row r="89" ht="64" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>法律上、身体拘束に関する記録は義務付けられており、専用の様式を用いてその態様及び時間・その際の利用者の心身の状況・やむを得なかった理由などを記録します。身体拘束の早期解除に向けて、拘束の必要性や方法を逐次検討します。その記録は5年間保存し、行政担当部局の運営指導等が行われる際に提示できるようにします。</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="6" customHeight="1"/>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
+    <row r="90" ht="6" customHeight="1"/>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>4）拘束の解除</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="32" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>3）の記録と再検討の結果、身体拘束を継続する必要性がなくなった場合は、速やかに身体拘束を解除します。その場合には、契約者、家族、居宅介護支援事業所に報告します。</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="10" customHeight="1"/>
-    <row r="93" ht="26" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
+    <row r="93" ht="10" customHeight="1"/>
+    <row r="94" ht="26" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>5．身体的拘束等の報告方法等のための方策に関する基本方針</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="32" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　1）身体的拘束等を行う場合には、4．の手続きに基づき利用者家族に速やかに説明し、報告を行うこと。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="48" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　2）訪問先等において他の職員等による適切な手続きに依らない身体的拘束等を視認等した場合、具体的な状況、時刻等を確認したうえで委員会への報告を行うこと。当該報告を受けた委員は、身体的拘束を実施したと思われる職員に聞き取りを行い実態の把握に努めること。</t>
         </is>
       </c>
     </row>
     <row r="96" ht="48" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　2）訪問先等において他の職員等による適切な手続きに依らない身体的拘束等を視認等した場合、具体的な状況、時刻等を確認したうえで委員会への報告を行うこと。当該報告を受けた委員は、身体的拘束を実施したと思われる職員に聞き取りを行い実態の把握に努めること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="48" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　3）適切な手続きに依らない身体的拘束の事実が判明した場合は、利用者及び利用者家族への謝罪を行い、大阪市への報告を行うこと。高齢者虐待に該当するおそれがある場合は、高齢者虐待防止法に基づき通報すること。</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="32" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
+    <row r="98" ht="32" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　4）訪問時に家族等による身体拘束を発見した場合は、管理者に報告し、居宅介護支援事業所と連携して対応すること。</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="8" customHeight="1"/>
-    <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
+    <row r="99" ht="8" customHeight="1"/>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>介護保険指定基準において身体拘束禁止の対象となる具体的な行為</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（1）徘徊しないように、車椅子や椅子・ベッドに体幹や四肢をひも等で縛る</t>
         </is>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（2）転落しないように、ベッドに体幹や四肢をひも等で縛る</t>
+          <t xml:space="preserve">　（1）徘徊しないように、車椅子や椅子・ベッドに体幹や四肢をひも等で縛る</t>
         </is>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（3）自分で降りられないように、ベッドを柵（サイドレール）で囲む</t>
+          <t xml:space="preserve">　（2）転落しないように、ベッドに体幹や四肢をひも等で縛る</t>
         </is>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　（3）自分で降りられないように、ベッドを柵（サイドレール）で囲む</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　（4）点滴・経管栄養等のチューブを抜かないように、四肢をひも等で縛る</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="32" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（5）点滴・経管栄養等のチューブを抜かないように、又は皮膚をかきむしらないように、手指の機能を制限するミトン型の手袋等をつける</t>
         </is>
       </c>
     </row>
     <row r="105" ht="32" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　（5）点滴・経管栄養等のチューブを抜かないように、又は皮膚をかきむしらないように、手指の機能を制限するミトン型の手袋等をつける</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="32" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　（6）車椅子・椅子からずり落ちたり、立ち上がったりしないように、Y字型拘束帯や腰ベルト・車椅子テーブルをつける</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（7）立ち上がる能力のある人の立ち上がりを妨げるような椅子を使用する</t>
         </is>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（8）脱衣やオムツはずしを制限するために、介護衣（つなぎ服）を着せる</t>
+          <t xml:space="preserve">　（7）立ち上がる能力のある人の立ち上がりを妨げるような椅子を使用する</t>
         </is>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（9）他人への迷惑行為を防ぐために、ベッドなどに体幹や四肢をひも等で縛る</t>
+          <t xml:space="preserve">　（8）脱衣やオムツはずしを制限するために、介護衣（つなぎ服）を着せる</t>
         </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（10）行動を落ち着かせるために、向精神薬を過剰に服用させる</t>
+          <t xml:space="preserve">　（9）他人への迷惑行為を防ぐために、ベッドなどに体幹や四肢をひも等で縛る</t>
         </is>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　（10）行動を落ち着かせるために、向精神薬を過剰に服用させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　（11）自分の意思で開けることのできない居室等に隔離する</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="8" customHeight="1"/>
-    <row r="112" ht="26" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
+    <row r="112" ht="8" customHeight="1"/>
+    <row r="113" ht="26" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>6．身体拘束廃止に向けた各職種の役割</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="32" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
+    <row r="114" ht="32" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>身体拘束の廃止のために、各職種の専門性に基づくアプローチから、チームケアを行うことを基本とし、それぞれの果たすべき役割に責任をもって対応します。</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="6" customHeight="1"/>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="7" t="inlineStr">
+    <row r="115" ht="6" customHeight="1"/>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
         <is>
           <t>（代表取締役）</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1）身体拘束における諸課題等の最高責任者</t>
         </is>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　2）委員会総括責任者</t>
+          <t xml:space="preserve">　1）身体拘束における諸課題等の最高責任者</t>
         </is>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　2）委員会総括責任者</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　3）家族、医療、行政機関、その他関係機関への対応</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="8" customHeight="1"/>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="7" t="inlineStr">
+    <row r="120" ht="8" customHeight="1"/>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="7" t="inlineStr">
         <is>
           <t>（身体拘束適正化委員会）</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1）身体拘束廃止のための指針の周知徹底</t>
         </is>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　2）身体拘束に関する説明書、システムの確立</t>
+          <t xml:space="preserve">　1）身体拘束廃止のための指針の周知徹底</t>
         </is>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　3）身体拘束に関する対応策及び防止策の検討</t>
+          <t xml:space="preserve">　2）身体拘束に関する説明書、システムの確立</t>
         </is>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　4）検討内容の実践、結果確認及び再検討</t>
+          <t xml:space="preserve">　3）身体拘束に関する対応策及び防止策の検討</t>
         </is>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　4）検討内容の実践、結果確認及び再検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　5）身体拘束廃止に向けた職員教育</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="8" customHeight="1"/>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="7" t="inlineStr">
+    <row r="127" ht="8" customHeight="1"/>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="7" t="inlineStr">
         <is>
           <t>（全従業者）</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1）拘束がもたらす弊害を正確に認識する</t>
         </is>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　2）利用者の尊厳を理解する</t>
+          <t xml:space="preserve">　1）拘束がもたらす弊害を正確に認識する</t>
         </is>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　3）利用者の疾病、障害等による行動特性の理解</t>
+          <t xml:space="preserve">　2）利用者の尊厳を理解する</t>
         </is>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　4）利用者個々の心身の状態を把握し、基本的ケアに努める</t>
+          <t xml:space="preserve">　3）利用者の疾病、障害等による行動特性の理解</t>
         </is>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　5）利用者とのコミュニケーションを充分にとる</t>
+          <t xml:space="preserve">　4）利用者個々の心身の状態を把握し、基本的ケアに努める</t>
         </is>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　6）記録は正確かつ丁寧に記録する</t>
+          <t xml:space="preserve">　5）利用者とのコミュニケーションを充分にとる</t>
         </is>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　7）医療機関、家族、居宅介護支援事業所等の関係機関との連絡調整</t>
+          <t xml:space="preserve">　6）記録は正確かつ丁寧に記録する</t>
         </is>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　8）訪問介護員が行える医療的ケアの範囲の確認</t>
+          <t xml:space="preserve">　7）医療機関、家族、居宅介護支援事業所等の関係機関との連絡調整</t>
         </is>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　9）重度化する利用者の状態観察</t>
+          <t xml:space="preserve">　8）訪問介護員が行える医療的ケアの範囲の確認</t>
         </is>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　10）家族の意向に添ったケアの確立</t>
+          <t xml:space="preserve">　9）重度化する利用者の状態観察</t>
         </is>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　10）家族の意向に添ったケアの確立</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　11）利用者宅の住環境（段差・家具配置等）や福祉用具の改善提案</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="8" customHeight="1"/>
-    <row r="140" ht="26" customHeight="1">
-      <c r="A140" s="4" t="inlineStr">
+    <row r="140" ht="8" customHeight="1"/>
+    <row r="141" ht="26" customHeight="1">
+      <c r="A141" s="4" t="inlineStr">
         <is>
           <t>7．身体拘束廃止・改善のための職員教育・研修</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="32" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
+    <row r="142" ht="32" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>支援に携わる全ての職員（登録ヘルパーを含む）に対して、身体拘束廃止と人権を尊重したケアの励行を図り、事故防止と合わせてリスクマネジメントとしての職員教育を行います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　① 定期的な教育・研修（年2回）の実施</t>
         </is>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　② 新任者に対する身体拘束廃止・改善のための研修の実施</t>
+          <t xml:space="preserve">　① 定期的な教育・研修（年2回）の実施</t>
         </is>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　② 新任者に対する身体拘束廃止・改善のための研修の実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　③ その他必要な教育・研修の実施</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="8" customHeight="1"/>
-    <row r="146" ht="26" customHeight="1">
-      <c r="A146" s="4" t="inlineStr">
+    <row r="146" ht="8" customHeight="1"/>
+    <row r="147" ht="26" customHeight="1">
+      <c r="A147" s="4" t="inlineStr">
         <is>
           <t>8．身体拘束廃止に関する指針の閲覧について</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="32" customHeight="1">
-      <c r="A147" s="5" t="inlineStr">
+    <row r="148" ht="32" customHeight="1">
+      <c r="A148" s="5" t="inlineStr">
         <is>
           <t>この指針は、当事業所内に掲示するとともに、利用者・家族がいつでも自由に閲覧することができます。</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="10" customHeight="1"/>
-    <row r="149" ht="26" customHeight="1">
-      <c r="A149" s="4" t="inlineStr">
+    <row r="149" ht="10" customHeight="1"/>
+    <row r="150" ht="26" customHeight="1">
+      <c r="A150" s="4" t="inlineStr">
         <is>
           <t>9．附則</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="5" t="inlineStr">
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="5" t="inlineStr">
         <is>
           <t>この指針は令和8年2月1日より施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="104">
+  <mergeCells count="105">
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A142:E142"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="A94:E94"/>
     <mergeCell ref="A103:E103"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A87:E87"/>
     <mergeCell ref="A128:E128"/>
     <mergeCell ref="A137:E137"/>
     <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A89:E89"/>
     <mergeCell ref="A136:E136"/>
     <mergeCell ref="A105:E105"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A139:E139"/>
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="A129:E129"/>
     <mergeCell ref="A91:E91"/>
@@ -1271,21 +1278,21 @@
     <mergeCell ref="A100:E100"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A115:E115"/>
-    <mergeCell ref="A93:E93"/>
     <mergeCell ref="A130:E130"/>
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A148:E148"/>
     <mergeCell ref="A49:E49"/>
     <mergeCell ref="A138:E138"/>
     <mergeCell ref="A132:E132"/>
     <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A119:E119"/>
     <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A78:E78"/>
     <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A75:E75"/>
     <mergeCell ref="A133:E133"/>
     <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A120:E120"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A104:E104"/>
     <mergeCell ref="A32:E32"/>
@@ -1299,33 +1306,34 @@
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
     <mergeCell ref="A60:E60"/>
     <mergeCell ref="A123:E123"/>
     <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A146:E146"/>
     <mergeCell ref="A124:E124"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A108:E108"/>
     <mergeCell ref="A84:E84"/>
     <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A149:E149"/>
     <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A86:E86"/>
     <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A151:E151"/>
     <mergeCell ref="A141:E141"/>
     <mergeCell ref="A135:E135"/>
     <mergeCell ref="A150:E150"/>
     <mergeCell ref="A144:E144"/>
     <mergeCell ref="A122:E122"/>
     <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A72:E72"/>
     <mergeCell ref="A134:E134"/>
-    <mergeCell ref="A112:E112"/>
     <mergeCell ref="A121:E121"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A127:E127"/>
     <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A114:E114"/>
     <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A98:E98"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A107:E107"/>
     <mergeCell ref="A61:E61"/>
@@ -1333,17 +1341,15 @@
     <mergeCell ref="A70:E70"/>
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A99:E99"/>
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A145:E145"/>
     <mergeCell ref="A101:E101"/>
-    <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A85:E85"/>
     <mergeCell ref="A116:E116"/>
-    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A126:E126"/>
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A35:E35"/>
@@ -1351,7 +1357,9 @@
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A102:E102"/>
     <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
     <mergeCell ref="A143:E143"/>
+    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/身体拘束廃止に関する指針_いいかいご.xlsx
+++ b/output/身体拘束廃止に関する指針_いいかいご.xlsx
@@ -772,7 +772,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・訪問介護員　松村 知恵</t>
+          <t xml:space="preserve">　・看護職　松村 知恵</t>
         </is>
       </c>
     </row>

--- a/output/身体拘束廃止に関する指針_いいかいご.xlsx
+++ b/output/身体拘束廃止に関する指針_いいかいご.xlsx
@@ -779,7 +779,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・訪問介護員（ヘルパー代表）　WIN YADANAR AWNG</t>
+          <t xml:space="preserve">　・訪問介護員（ヘルパー代表）　WIN YADANAR AUNG</t>
         </is>
       </c>
     </row>

--- a/output/身体拘束廃止に関する指針_いいかいご.xlsx
+++ b/output/身体拘束廃止に関する指針_いいかいご.xlsx
@@ -758,7 +758,7 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・代表取締役（法人代表者）　吉田 俊輔</t>
+          <t xml:space="preserve">　・代表取締役（法人代表者）　吉田 駿成</t>
         </is>
       </c>
     </row>
